--- a/stories/arbres/TREE-REL-017.xlsx
+++ b/stories/arbres/TREE-REL-017.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la ferme avec papa. Un camarade trébuche dans la paille. Quelqu'un veut rire. Léa dit : pas rire. Pas répéter. Ce n'est pas gentil. Léa tend la main. Maman arrive.</t>
+          <t>Léa est à la ferme avec papa. Un camarade trébuche dans la paille. Quelqu'un veut rire. Pas rire. Pas répéter. Ce n'est pas gentil. Léa tend la main. Maman arrive.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est à la ferme avec papa. Un camarade trébuche dans la paille. Quelqu'un veut rire.
+enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil.
+narrateur|Léa tend la main. Maman arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers la cuisine. Une feuille tombe. Un camarade trébuche. Léa dit : pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+          <t>Léa va vers la cuisine. Une feuille tombe. Un camarade trébuche. Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Une feuille tombe. Un camarade trébuche.
+enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2232,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2399,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2590,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2757,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2924,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3091,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. On entend un oiseau. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3258,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3425,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Ça sent l'herbe coupée. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3592,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3759,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3950,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4117,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. On entend un oiseau. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Ça sent l'herbe coupée. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le soleil chauffe un peu. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5119,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5310,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5477,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5644,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5811,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5978,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6145,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le sol est frais. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6312,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6341,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le jardin. Le vent est doux. Un camarade trébuche. Léa dit : pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+          <t>Léa va vers le jardin. Le vent est doux. Un camarade trébuche. Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6479,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. Le vent est doux. Un camarade trébuche.
+enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7029,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7196,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7387,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. On entend un oiseau. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Ça sent l'herbe coupée. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le soleil chauffe un peu. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8747,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8914,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9081,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9248,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9415,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9582,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le sol est frais. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9749,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9916,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10107,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10274,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le soleil chauffe un peu. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10441,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10608,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le sol est frais. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10775,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10942,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un petit bruit d'eau. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11109,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11138,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers la chambre. On entend un oiseau. Un camarade trébuche. Léa dit : pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+          <t>Léa va vers la chambre. On entend un oiseau. Un camarade trébuche. Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11276,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. On entend un oiseau. Un camarade trébuche.
+enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11499,6 +11826,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11661,6 +11993,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12184,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12351,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12518,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12685,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12852,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13019,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le sol est frais. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13353,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13544,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13711,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le soleil chauffe un peu. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13878,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14045,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le sol est frais. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14212,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14379,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un petit bruit d'eau. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14546,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14713,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15071,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le sol est frais. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15238,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15405,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un petit bruit d'eau. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Les chaussures font toc toc. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15906,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15494,6 +15946,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-017.xlsx
+++ b/stories/arbres/TREE-REL-017.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Léa tend la main. Maman arrive.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1688,6 +1695,7 @@
 enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2237,6 +2247,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2404,6 +2415,7 @@
           <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2595,6 +2607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2762,6 +2775,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2929,6 +2943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,6 +3111,7 @@
           <t>narrateur|C'est après la sieste. On entend un oiseau. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3263,6 +3279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3430,6 +3447,7 @@
           <t>narrateur|C'est le soir. Ça sent l'herbe coupée. Dans la cuisine, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3597,6 +3615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3764,6 +3783,7 @@
           <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3955,6 +3975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4143,7 @@
           <t>narrateur|C'est le matin. On entend un oiseau. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4479,7 @@
           <t>narrateur|C'est après la sieste. Ça sent l'herbe coupée. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4815,7 @@
           <t>narrateur|C'est le soir. Le soleil chauffe un peu. Dans la cuisine, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5151,7 @@
           <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5315,6 +5343,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5482,6 +5511,7 @@
           <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5649,6 +5679,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5816,6 +5847,7 @@
           <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5983,6 +6015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6150,6 +6183,7 @@
           <t>narrateur|C'est le soir. Le sol est frais. Dans la cuisine, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6317,6 +6351,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,7 @@
 enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7072,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7201,6 +7240,7 @@
           <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7600,7 @@
           <t>narrateur|C'est le matin. On entend un oiseau. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7936,7 @@
           <t>narrateur|C'est après la sieste. Ça sent l'herbe coupée. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8272,7 @@
           <t>narrateur|C'est le soir. Le soleil chauffe un peu. Dans le jardin, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8608,7 @@
           <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8752,6 +8800,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8919,6 +8968,7 @@
           <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9086,6 +9136,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9253,6 +9304,7 @@
           <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9420,6 +9472,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9587,6 +9640,7 @@
           <t>narrateur|C'est le soir. Le sol est frais. Dans le jardin, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9754,6 +9808,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9921,6 +9976,7 @@
           <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10112,6 +10168,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10279,6 +10336,7 @@
           <t>narrateur|C'est le matin. Le soleil chauffe un peu. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10446,6 +10504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10613,6 +10672,7 @@
           <t>narrateur|C'est après la sieste. Le sol est frais. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10780,6 +10840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10947,6 +11008,7 @@
           <t>narrateur|C'est le soir. Un petit bruit d'eau. Dans le jardin, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11114,6 +11176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,7 @@
 enfant-f|Pas rire. Pas répéter. Ce n'est pas gentil. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11529,7 @@
           <t>narrateur|Un camarade trébuche. Léa fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11701,7 @@
           <t>narrateur|Oui. Pas rire. Pas répéter. Pas gentil. Léa a retenu. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11831,6 +11897,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11998,6 +12065,7 @@
           <t>narrateur|Léa propose les cubes. Le sol est frais. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12189,6 +12257,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12356,6 +12425,7 @@
           <t>narrateur|C'est le matin. Ça sent l'herbe coupée. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12523,6 +12593,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12690,6 +12761,7 @@
           <t>narrateur|C'est après la sieste. Le soleil chauffe un peu. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12857,6 +12929,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13024,6 +13097,7 @@
           <t>narrateur|C'est le soir. Le sol est frais. Dans la chambre, avec les cubes. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13191,6 +13265,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13358,6 +13433,7 @@
           <t>narrateur|Léa propose le livre. Un petit bruit d'eau. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13549,6 +13625,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13716,6 +13793,7 @@
           <t>narrateur|C'est le matin. Le soleil chauffe un peu. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13883,6 +13961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14050,6 +14129,7 @@
           <t>narrateur|C'est après la sieste. Le sol est frais. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14217,6 +14297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14384,6 +14465,7 @@
           <t>narrateur|C'est le soir. Un petit bruit d'eau. Dans la chambre, avec le livre. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14551,6 +14633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14718,6 +14801,7 @@
           <t>narrateur|Léa propose la dînette. Les chaussures font toc toc. On joue. Pas rire. Pas répéter. Ce n'est pas gentil. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14909,6 +14993,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15076,6 +15161,7 @@
           <t>narrateur|C'est le matin. Le sol est frais. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15243,6 +15329,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15410,6 +15497,7 @@
           <t>narrateur|C'est après la sieste. Un petit bruit d'eau. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15577,6 +15665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15744,6 +15833,7 @@
           <t>narrateur|C'est le soir. Les chaussures font toc toc. Dans la chambre, avec la dînette. Léa répète : pas rire. Pas répéter. Ce n'est pas gentil. Léa dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15911,6 +16001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15929,7 +16020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15953,6 +16044,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15967,7 +16072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16154,6 +16259,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
